--- a/Joaquin/Matriz_Joaquin.xlsx
+++ b/Joaquin/Matriz_Joaquin.xlsx
@@ -415,6 +415,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Claude (revisión 07-10-2026)</author>
+    <author>Claude (pre-evaluación 10-10-2026)</author>
   </authors>
   <commentList>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -427,9 +428,10 @@
         <t>Leído completo. ASXAML: XGBoost + RFECV + Optuna para suprimir alertas falsas de un sistema de reglas. Datos reales de un banco (Egipto), 46 escenarios, 210 996 clientes con alertas, 6 meses. F-beta 0,86, recall 0,92, reduce 73 % de falsos positivos. Supervisado: requiere etiquetas del analista. Cuartil: pendiente.</t>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0">
+    <comment ref="E7" authorId="1" shapeId="0">
       <text>
-        <t>PDF no descargado (ScienceDirect bloquea la descarga automática): bajar desde la biblioteca UPC. DOI corregido (antes estaba el enlace PII). País según afiliación en Scopus: Strathmore University, Kenia.</t>
+        <t>PDF no descargado (ScienceDirect bloquea la descarga automática): bajar desde la biblioteca UPC. DOI corregido (antes estaba el enlace PII). País según afiliación en Scopus: Strathmore University, Kenia.
+PRE-EVALUACIÓN (solo resumen; PDF bloqueado aunque es de acceso abierto): FUERTE. Aporte propio (VAE + GNN + reglas) validado con 54 258 transacciones transfronterizas REALES de un banco de África Oriental + validación independiente en otra entidad de Kenia. No supervisado: One-Class SVM supera a Isolation Forest y LOF, precisión 99,63 % en el 5 % superior de alertas priorizadas (análogo directo al IE10 del proyecto). Cumple CI1, CI3, CI4, CI5; no cae en CE1-CE4. Falta: cuartil y confirmar en el texto completo.</t>
       </text>
     </comment>
     <comment ref="E8" authorId="0" shapeId="0">

--- a/Joaquin/Matriz_Joaquin.xlsx
+++ b/Joaquin/Matriz_Joaquin.xlsx
@@ -415,7 +415,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Claude (revisión 07-10-2026)</author>
-    <author>Claude (pre-evaluación 10-10-2026)</author>
+    <author>Claude (lectura completa 10-10-2026)</author>
   </authors>
   <commentList>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -431,7 +431,8 @@
     <comment ref="E7" authorId="1" shapeId="0">
       <text>
         <t>PDF no descargado (ScienceDirect bloquea la descarga automática): bajar desde la biblioteca UPC. DOI corregido (antes estaba el enlace PII). País según afiliación en Scopus: Strathmore University, Kenia.
-PRE-EVALUACIÓN (solo resumen; PDF bloqueado aunque es de acceso abierto): FUERTE. Aporte propio (VAE + GNN + reglas) validado con 54 258 transacciones transfronterizas REALES de un banco de África Oriental + validación independiente en otra entidad de Kenia. No supervisado: One-Class SVM supera a Isolation Forest y LOF, precisión 99,63 % en el 5 % superior de alertas priorizadas (análogo directo al IE10 del proyecto). Cumple CI1, CI3, CI4, CI5; no cae en CE1-CE4. Falta: cuartil y confirmar en el texto completo.</t>
+PRE-EVALUACIÓN (solo resumen; PDF bloqueado aunque es de acceso abierto): FUERTE. Aporte propio (VAE + GNN + reglas) validado con 54 258 transacciones transfronterizas REALES de un banco de África Oriental + validación independiente en otra entidad de Kenia. No supervisado: One-Class SVM supera a Isolation Forest y LOF, precisión 99,63 % en el 5 % superior de alertas priorizadas (análogo directo al IE10 del proyecto). Cumple CI1, CI3, CI4, CI5; no cae en CE1-CE4. Falta: cuartil y confirmar en el texto completo.
+LECTURA COMPLETA: CUMPLE (falta cuartil). 54 258 pagos SWIFT reales de un banco de África Oriental (9 meses de 2024). Variables útiles para Perumoney: días desde la operación anterior, antigüedad del cliente, desviación del monto respecto a su promedio, volatilidad, país de alto riesgo y bandera de fraccionamiento (&lt;10k). One-Class SVM entrenado SOLO con operaciones no marcadas (no requiere etiquetas): P@5% 99,26 % en test, AP 0,85, ROC 0,85; supera a Isolation Forest (P@5% 83,99 %). Ablación: sin embeddings GNN o VAE el AP cae. Validado operativamente en otra entidad de Kenia (1000 tps). OJO: la 'verdad' para evaluar son las propias reglas (proxy), no ROS confirmados; los autores lo reconocen. Responde P2, P3, P4, P5. Código y datos: github.com/cokungu1/TT</t>
       </text>
     </comment>
     <comment ref="E8" authorId="0" shapeId="0">
@@ -1134,7 +1135,7 @@
       <c r="K7" s="38" t="n"/>
       <c r="L7" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M7" s="39" t="inlineStr">

--- a/Joaquin/Matriz_Joaquin.xlsx
+++ b/Joaquin/Matriz_Joaquin.xlsx
@@ -435,9 +435,10 @@
 LECTURA COMPLETA: CUMPLE (falta cuartil). 54 258 pagos SWIFT reales de un banco de África Oriental (9 meses de 2024). Variables útiles para Perumoney: días desde la operación anterior, antigüedad del cliente, desviación del monto respecto a su promedio, volatilidad, país de alto riesgo y bandera de fraccionamiento (&lt;10k). One-Class SVM entrenado SOLO con operaciones no marcadas (no requiere etiquetas): P@5% 99,26 % en test, AP 0,85, ROC 0,85; supera a Isolation Forest (P@5% 83,99 %). Ablación: sin embeddings GNN o VAE el AP cae. Validado operativamente en otra entidad de Kenia (1000 tps). OJO: la 'verdad' para evaluar son las propias reglas (proxy), no ROS confirmados; los autores lo reconocen. Responde P2, P3, P4, P5. Código y datos: github.com/cokungu1/TT</t>
       </text>
     </comment>
-    <comment ref="E8" authorId="0" shapeId="0">
+    <comment ref="E8" authorId="1" shapeId="0">
       <text>
-        <t>PDF no disponible en acceso abierto (IEEE, de pago): bajar desde la biblioteca UPC. País pendiente: no figura la afiliación en la lista de candidatos.</t>
+        <t>PDF no disponible en acceso abierto (IEEE, de pago): bajar desde la biblioteca UPC. País pendiente: no figura la afiliación en la lista de candidatos.
+LECTURA COMPLETA: CUMPLE (falta cuartil). Qilu University of Technology, China. MLaD2: red de relaciones entre cuentas por similitud + GNN + pre-entrenamiento autosupervisado contrastivo y ajuste fino con pocas etiquetas. Datos reales de una agencia policial china (caso de juego ilegal, 51 326 transacciones). Con solo 10 % de etiquetas supera a XGBoost (+2,7 % F1), GAT/EvolveGCN y a no supervisados (FlowScope, MonLAD: +24,8 % F1). Respalda lo que el Cap. 1 le atribuye (menor dependencia de etiquetas). Limitaciones (de los autores): un solo dataset pequeño y antiguo, poca interpretabilidad; requiere grafo de transferencias entre cuentas (Perumoney no lo tiene) y algunas etiquetas. Responde P3, P4, P5.</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
@@ -1207,11 +1208,15 @@
           <t>https://doi.org/10.1109/TIFS.2024.3380262</t>
         </is>
       </c>
-      <c r="J8" s="37" t="n"/>
+      <c r="J8" s="37" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
       <c r="K8" s="38" t="n"/>
       <c r="L8" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M8" s="39" t="inlineStr">

--- a/Joaquin/Matriz_Joaquin.xlsx
+++ b/Joaquin/Matriz_Joaquin.xlsx
@@ -416,6 +416,7 @@
   <authors>
     <author>Claude (revisión 07-10-2026)</author>
     <author>Claude (lectura completa 10-10-2026)</author>
+    <author>Claude (10-10-2026)</author>
   </authors>
   <commentList>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -444,6 +445,16 @@
     <comment ref="E9" authorId="0" shapeId="0">
       <text>
         <t>Leído completo (versión aceptada del autor, repositorio NTNU). Datos reales de BN Bank (Noruega), PYMES, 500 767 observaciones, 2021-2023. XGBoost/LGBM/HistGB; AUC 0,94 combinando datos bancarios + crédito + contables (solo bancarios: 0,81-0,85). Clasificación de riesgo del CLIENTE. Limitación para Perumoney: usa datos contables y de crédito de empresas, que una casa de cambio no tiene de personas naturales. Cuartil: pendiente.</t>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="2" shapeId="0">
+      <text>
+        <t>Leído completo; cumple CI1-CI5 y no cae en CE1-CE4. Falta verificar cuartil en Scimago (columna K). Viene de Candidatos_Joaquin.xlsx fila 19.</t>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="2" shapeId="0">
+      <text>
+        <t>Leído completo; cumple CI1-CI5 y no cae en CE1-CE4. Falta verificar cuartil en Scimago (columna K). Viene de Candidatos_Joaquin.xlsx fila 21.</t>
       </text>
     </comment>
   </commentList>
@@ -1336,17 +1347,43 @@
           <t>Joaquín</t>
         </is>
       </c>
-      <c r="D10" s="37" t="n"/>
-      <c r="E10" s="37" t="n"/>
-      <c r="F10" s="37" t="n"/>
-      <c r="G10" s="38" t="n"/>
-      <c r="H10" s="37" t="n"/>
-      <c r="I10" s="37" t="n"/>
-      <c r="J10" s="37" t="n"/>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>Banco o entidad financiera</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>GCF-MLD: Integrated Approach for Money Laundering Detection Using Machine Learning and Graph Network Analysis</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>Irshad, Alkhalifah, Alturise y Khan</t>
+        </is>
+      </c>
+      <c r="G10" s="38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H10" s="37" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="I10" s="37" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/ACCESS.2024.3510115</t>
+        </is>
+      </c>
+      <c r="J10" s="37" t="inlineStr">
+        <is>
+          <t>Pakistán</t>
+        </is>
+      </c>
       <c r="K10" s="38" t="n"/>
       <c r="L10" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M10" s="39" t="n"/>
@@ -1378,17 +1415,43 @@
           <t>Joaquín</t>
         </is>
       </c>
-      <c r="D11" s="37" t="n"/>
-      <c r="E11" s="37" t="n"/>
-      <c r="F11" s="37" t="n"/>
-      <c r="G11" s="38" t="n"/>
-      <c r="H11" s="37" t="n"/>
-      <c r="I11" s="37" t="n"/>
-      <c r="J11" s="37" t="n"/>
+      <c r="D11" s="37" t="inlineStr">
+        <is>
+          <t>Banco o entidad financiera</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>Incorporating machine learning and a risk-based strategy in an anti-money laundering multiagent system</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>Alexandre y Balsa</t>
+        </is>
+      </c>
+      <c r="G11" s="38" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H11" s="37" t="inlineStr">
+        <is>
+          <t>Expert Systems with Applications</t>
+        </is>
+      </c>
+      <c r="I11" s="37" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.eswa.2023.119500</t>
+        </is>
+      </c>
+      <c r="J11" s="37" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
       <c r="K11" s="38" t="n"/>
       <c r="L11" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M11" s="39" t="n"/>

--- a/Joaquin/Matriz_Joaquin.xlsx
+++ b/Joaquin/Matriz_Joaquin.xlsx
@@ -1448,7 +1448,11 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="K11" s="38" t="n"/>
+      <c r="K11" s="38" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="L11" s="38" t="inlineStr">
         <is>
           <t>Sí</t>

--- a/Joaquin/Matriz_Joaquin.xlsx
+++ b/Joaquin/Matriz_Joaquin.xlsx
@@ -415,8 +415,8 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Claude (revisión 07-10-2026)</author>
+    <author>Claude (10-10-2026)</author>
     <author>Claude (lectura completa 10-10-2026)</author>
-    <author>Claude (10-10-2026)</author>
   </authors>
   <commentList>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -424,22 +424,42 @@
         <t>SE MANTIENE CON NOTA. Leído completo. Ojo: (1) no compara contra sistemas de reglas; (2) el mejor modelo es XGBoost (supervisado), Isolation Forest tiene AUC 0,62; (3) usa el dataset IBM AML de Kaggle (sintético) aunque lo llama 'real' y dice que está balanceado; (4) accuracy 1,00 y AUC de XGBoost se reporta como 0,94 y 0,62 en distintas partes. Corregir lo que el Cap. 1 le atribuye ('anomalías superan a reglas simples'). Cuartil: pendiente.</t>
       </text>
     </comment>
+    <comment ref="K5" authorId="1" shapeId="0">
+      <text>
+        <t>Discover Artificial Intelligence 2025: Q1 en sus 4 categorías (Artificial Intelligence, Information Systems...). Captura en Capturas_Scimago/.</t>
+      </text>
+    </comment>
     <comment ref="E6" authorId="0" shapeId="0">
       <text>
         <t>Leído completo. ASXAML: XGBoost + RFECV + Optuna para suprimir alertas falsas de un sistema de reglas. Datos reales de un banco (Egipto), 46 escenarios, 210 996 clientes con alertas, 6 meses. F-beta 0,86, recall 0,92, reduce 73 % de falsos positivos. Supervisado: requiere etiquetas del analista. Cuartil: pendiente.</t>
       </text>
     </comment>
-    <comment ref="E7" authorId="1" shapeId="0">
+    <comment ref="K6" authorId="1" shapeId="0">
+      <text>
+        <t>The Journal of Supercomputing 2023-2024: Q2 en Information Systems, Software, Hardware and Architecture y Theoretical CS. Captura en Capturas_Scimago/.</t>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="2" shapeId="0">
       <text>
         <t>PDF no descargado (ScienceDirect bloquea la descarga automática): bajar desde la biblioteca UPC. DOI corregido (antes estaba el enlace PII). País según afiliación en Scopus: Strathmore University, Kenia.
 PRE-EVALUACIÓN (solo resumen; PDF bloqueado aunque es de acceso abierto): FUERTE. Aporte propio (VAE + GNN + reglas) validado con 54 258 transacciones transfronterizas REALES de un banco de África Oriental + validación independiente en otra entidad de Kenia. No supervisado: One-Class SVM supera a Isolation Forest y LOF, precisión 99,63 % en el 5 % superior de alertas priorizadas (análogo directo al IE10 del proyecto). Cumple CI1, CI3, CI4, CI5; no cae en CE1-CE4. Falta: cuartil y confirmar en el texto completo.
 LECTURA COMPLETA: CUMPLE (falta cuartil). 54 258 pagos SWIFT reales de un banco de África Oriental (9 meses de 2024). Variables útiles para Perumoney: días desde la operación anterior, antigüedad del cliente, desviación del monto respecto a su promedio, volatilidad, país de alto riesgo y bandera de fraccionamiento (&lt;10k). One-Class SVM entrenado SOLO con operaciones no marcadas (no requiere etiquetas): P@5% 99,26 % en test, AP 0,85, ROC 0,85; supera a Isolation Forest (P@5% 83,99 %). Ablación: sin embeddings GNN o VAE el AP cae. Validado operativamente en otra entidad de Kenia (1000 tps). OJO: la 'verdad' para evaluar son las propias reglas (proxy), no ROS confirmados; los autores lo reconocen. Responde P2, P3, P4, P5. Código y datos: github.com/cokungu1/TT</t>
       </text>
     </comment>
-    <comment ref="E8" authorId="1" shapeId="0">
+    <comment ref="K7" authorId="1" shapeId="0">
+      <text>
+        <t>Machine Learning with Applications: 2026 aún no publicado; se usa 2025 = Q1 (Artificial Intelligence, Computer Science Applications, Information Systems). Captura en Capturas_Scimago/.</t>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="2" shapeId="0">
       <text>
         <t>PDF no disponible en acceso abierto (IEEE, de pago): bajar desde la biblioteca UPC. País pendiente: no figura la afiliación en la lista de candidatos.
 LECTURA COMPLETA: CUMPLE (falta cuartil). Qilu University of Technology, China. MLaD2: red de relaciones entre cuentas por similitud + GNN + pre-entrenamiento autosupervisado contrastivo y ajuste fino con pocas etiquetas. Datos reales de una agencia policial china (caso de juego ilegal, 51 326 transacciones). Con solo 10 % de etiquetas supera a XGBoost (+2,7 % F1), GAT/EvolveGCN y a no supervisados (FlowScope, MonLAD: +24,8 % F1). Respalda lo que el Cap. 1 le atribuye (menor dependencia de etiquetas). Limitaciones (de los autores): un solo dataset pequeño y antiguo, poca interpretabilidad; requiere grafo de transferencias entre cuentas (Perumoney no lo tiene) y algunas etiquetas. Responde P3, P4, P5.</t>
+      </text>
+    </comment>
+    <comment ref="K8" authorId="1" shapeId="0">
+      <text>
+        <t>IEEE Trans. on Information Forensics and Security 2024: Q1 (Computer Networks and Communications; Safety, Risk, Reliability and Quality). Captura en Capturas_Scimago/.</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
@@ -447,12 +467,17 @@
         <t>Leído completo (versión aceptada del autor, repositorio NTNU). Datos reales de BN Bank (Noruega), PYMES, 500 767 observaciones, 2021-2023. XGBoost/LGBM/HistGB; AUC 0,94 combinando datos bancarios + crédito + contables (solo bancarios: 0,81-0,85). Clasificación de riesgo del CLIENTE. Limitación para Perumoney: usa datos contables y de crédito de empresas, que una casa de cambio no tiene de personas naturales. Cuartil: pendiente.</t>
       </text>
     </comment>
-    <comment ref="E10" authorId="2" shapeId="0">
+    <comment ref="K9" authorId="1" shapeId="0">
+      <text>
+        <t>Journal of Money Laundering Control 2025: Q1 en Economics, Econometrics and Finance (misc.) y en Law; Q2 en Public Administration. Se toma la categoría de finanzas. Captura en Capturas_Scimago/.</t>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="1" shapeId="0">
       <text>
         <t>Leído completo; cumple CI1-CI5 y no cae en CE1-CE4. Falta verificar cuartil en Scimago (columna K). Viene de Candidatos_Joaquin.xlsx fila 19.</t>
       </text>
     </comment>
-    <comment ref="E11" authorId="2" shapeId="0">
+    <comment ref="E11" authorId="1" shapeId="0">
       <text>
         <t>Leído completo; cumple CI1-CI5 y no cae en CE1-CE4. Falta verificar cuartil en Scimago (columna K). Viene de Candidatos_Joaquin.xlsx fila 21.</t>
       </text>
@@ -988,7 +1013,11 @@
           <t>Sudáfrica</t>
         </is>
       </c>
-      <c r="K5" s="38" t="n"/>
+      <c r="K5" s="38" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="L5" s="38" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1068,7 +1097,11 @@
           <t>Egipto</t>
         </is>
       </c>
-      <c r="K6" s="38" t="n"/>
+      <c r="K6" s="38" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="L6" s="38" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1144,7 +1177,11 @@
           <t>Kenia</t>
         </is>
       </c>
-      <c r="K7" s="38" t="n"/>
+      <c r="K7" s="38" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="L7" s="38" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1224,7 +1261,11 @@
           <t>China</t>
         </is>
       </c>
-      <c r="K8" s="38" t="n"/>
+      <c r="K8" s="38" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="L8" s="38" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1300,7 +1341,11 @@
           <t>Noruega</t>
         </is>
       </c>
-      <c r="K9" s="38" t="n"/>
+      <c r="K9" s="38" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="L9" s="38" t="inlineStr">
         <is>
           <t>Sí</t>

--- a/Joaquin/Matriz_Joaquin.xlsx
+++ b/Joaquin/Matriz_Joaquin.xlsx
@@ -477,6 +477,11 @@
         <t>Leído completo; cumple CI1-CI5 y no cae en CE1-CE4. Falta verificar cuartil en Scimago (columna K). Viene de Candidatos_Joaquin.xlsx fila 19.</t>
       </text>
     </comment>
+    <comment ref="K10" authorId="1" shapeId="0">
+      <text>
+        <t>IEEE Access 2024: Q1 en Computer Science (misc.) y Engineering (misc.). Captura en Capturas_Scimago/.</t>
+      </text>
+    </comment>
     <comment ref="E11" authorId="1" shapeId="0">
       <text>
         <t>Leído completo; cumple CI1-CI5 y no cae en CE1-CE4. Falta verificar cuartil en Scimago (columna K). Viene de Candidatos_Joaquin.xlsx fila 21.</t>
@@ -1425,7 +1430,11 @@
           <t>Pakistán</t>
         </is>
       </c>
-      <c r="K10" s="38" t="n"/>
+      <c r="K10" s="38" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="L10" s="38" t="inlineStr">
         <is>
           <t>Sí</t>

--- a/Joaquin/Matriz_Joaquin.xlsx
+++ b/Joaquin/Matriz_Joaquin.xlsx
@@ -487,6 +487,11 @@
         <t>Leído completo; cumple CI1-CI5 y no cae en CE1-CE4. Falta verificar cuartil en Scimago (columna K). Viene de Candidatos_Joaquin.xlsx fila 21.</t>
       </text>
     </comment>
+    <comment ref="E12" authorId="1" shapeId="0">
+      <text>
+        <t>LECTURA COMPLETA: CUMPLE (Q1). Pese a decir 'fraud', predice eventos SAR (reporte de operación sospechosa de lavado) a partir de alertas SAM de un banco real de Taiwán, con escenarios definidos según la tipología oficial de LA/FT del regulador. Convierte transacciones irregulares de los 15 días hábiles previos en series regulares, autoencoder con self-attention + GNN de relaciones entre clientes + generación de casos (CVAE/WGAN) para el desbalance. Supervisado (etiqueta = decisión del área legal). Compara con XGBoost y redes profundas: AUPRC 27 % vs 0,66-22,15 % (SAR desde alertas) y 22,9 % vs 2,5-22 % (SAR fuera de alertas). Limitación: un solo banco; requiere relaciones entre clientes. Útil para P2 (variables de ventana temporal), P3, P4 y P5 (AUPRC con datos reales y desbalance). Viene de Candidatos_Joaquin.xlsx fila 39.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1541,17 +1546,47 @@
           <t>Joaquín</t>
         </is>
       </c>
-      <c r="D12" s="37" t="n"/>
-      <c r="E12" s="37" t="n"/>
-      <c r="F12" s="37" t="n"/>
-      <c r="G12" s="38" t="n"/>
-      <c r="H12" s="37" t="n"/>
-      <c r="I12" s="37" t="n"/>
-      <c r="J12" s="37" t="n"/>
-      <c r="K12" s="38" t="n"/>
+      <c r="D12" s="37" t="inlineStr">
+        <is>
+          <t>Banco o entidad financiera</t>
+        </is>
+      </c>
+      <c r="E12" s="37" t="inlineStr">
+        <is>
+          <t>Fund transfer fraud detection: Analyzing irregular transactions and customer relationships with self-attention and graph neural networks</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>Shih, Dai, Chen, Ti, Wang y Kuo</t>
+        </is>
+      </c>
+      <c r="G12" s="38" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H12" s="37" t="inlineStr">
+        <is>
+          <t>Expert Systems with Applications</t>
+        </is>
+      </c>
+      <c r="I12" s="37" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.eswa.2024.125211</t>
+        </is>
+      </c>
+      <c r="J12" s="37" t="inlineStr">
+        <is>
+          <t>Taiwán</t>
+        </is>
+      </c>
+      <c r="K12" s="38" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="L12" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M12" s="39" t="n"/>

--- a/Joaquin/Matriz_Joaquin.xlsx
+++ b/Joaquin/Matriz_Joaquin.xlsx
@@ -417,6 +417,7 @@
     <author>Claude (revisión 07-10-2026)</author>
     <author>Claude (10-10-2026)</author>
     <author>Claude (lectura completa 10-10-2026)</author>
+    <author>Claude (11-10-2026)</author>
   </authors>
   <commentList>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -490,6 +491,21 @@
     <comment ref="E12" authorId="1" shapeId="0">
       <text>
         <t>LECTURA COMPLETA: CUMPLE (Q1). Pese a decir 'fraud', predice eventos SAR (reporte de operación sospechosa de lavado) a partir de alertas SAM de un banco real de Taiwán, con escenarios definidos según la tipología oficial de LA/FT del regulador. Convierte transacciones irregulares de los 15 días hábiles previos en series regulares, autoencoder con self-attention + GNN de relaciones entre clientes + generación de casos (CVAE/WGAN) para el desbalance. Supervisado (etiqueta = decisión del área legal). Compara con XGBoost y redes profundas: AUPRC 27 % vs 0,66-22,15 % (SAR desde alertas) y 22,9 % vs 2,5-22 % (SAR fuera de alertas). Limitación: un solo banco; requiere relaciones entre clientes. Útil para P2 (variables de ventana temporal), P3, P4 y P5 (AUPRC con datos reales y desbalance). Viene de Candidatos_Joaquin.xlsx fila 39.</t>
+      </text>
+    </comment>
+    <comment ref="E13" authorId="3" shapeId="0">
+      <text>
+        <t>LECTURA COMPLETA: CUMPLE (IEEE Access 2025, Q1). Özyeğin Univ., Turquía. AMLPD: embeddings NO supervisados (PageRank personalizado + difusión) sobre el grafo de transacciones y luego un clasificador. Datos reales de un gran banco turco (~10 M nodos, 23 M aristas, 1 mes) + AMLSim (sintético) + 2 benchmarks. F1 0,85 en el grafo de 10 M nodos; supera a GNN supervisadas y a no supervisados (DBSCAN). Limitación: requiere grafo de transferencias entre cuentas (Perumoney no lo tiene). Responde P3, P4, P5.</t>
+      </text>
+    </comment>
+    <comment ref="E14" authorId="3" shapeId="0">
+      <text>
+        <t>LECTURA COMPLETA: CUMPLE en lo formal; falta cuartil (Forensic Science International: Digital Investigation). Univ. Federal de Bahía, Brasil. Datos REALES de una investigación de lavado del Ministerio Público de Sergipe (sistema SIMBA): 9 322 transacciones de 4 investigados, 767 cuentas destino. NO supervisado: detección de anomalías con GNN + comunidades, densidad y ciclos; K-means/K-prototypes para perfiles. Validación sin etiquetas con Silhouette (0,83) y Davies-Bouldin (1,59) en test, con validación cruzada. Relevante para P5 (cómo validar sin casos etiquetados) y P2/P3. Limitación: muestra pequeña (4 personas) y validación solo con métricas internas.</t>
+      </text>
+    </comment>
+    <comment ref="E15" authorId="3" shapeId="0">
+      <text>
+        <t>LECTURA COMPLETA: CUMPLE en lo formal; falta cuartil (Applied Intelligence). NTNU, Noruega. SMoTeF detecta FRACCIONAMIENTO (smurfing) con flujo temporal máximo respetando el orden de las transacciones; reduce los falsos positivos de los detectores de patrones en grafos. Evaluado inyectando patrones de smurfing en datos reales (Czech Financial Dataset, ~280 mil transacciones bancarias; DARPA; Enron), con precision/recall/F1 frente al estado del arte. Muy relevante para la causa C2 (operaciones fraccionadas bajo el umbral de USD 5 000). Limitación: los casos positivos son inyectados (sintéticos) y requiere grafo origen-destino.</t>
       </text>
     </comment>
   </commentList>
@@ -1618,17 +1634,47 @@
           <t>Joaquín</t>
         </is>
       </c>
-      <c r="D13" s="37" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="37" t="n"/>
-      <c r="G13" s="38" t="n"/>
-      <c r="H13" s="37" t="n"/>
-      <c r="I13" s="37" t="n"/>
-      <c r="J13" s="37" t="n"/>
-      <c r="K13" s="38" t="n"/>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t>Banco o entidad financiera</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>PageRank-Based Unsupervised Deep Vertex Representations for Anti-Money Laundering Detection</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>Gezici y Sefer</t>
+        </is>
+      </c>
+      <c r="G13" s="38" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H13" s="37" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="I13" s="37" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/ACCESS.2025.3634197</t>
+        </is>
+      </c>
+      <c r="J13" s="37" t="inlineStr">
+        <is>
+          <t>Turquía</t>
+        </is>
+      </c>
+      <c r="K13" s="38" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="L13" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M13" s="39" t="n"/>
@@ -1660,17 +1706,43 @@
           <t>Joaquín</t>
         </is>
       </c>
-      <c r="D14" s="37" t="n"/>
-      <c r="E14" s="37" t="n"/>
-      <c r="F14" s="37" t="n"/>
-      <c r="G14" s="38" t="n"/>
-      <c r="H14" s="37" t="n"/>
-      <c r="I14" s="37" t="n"/>
-      <c r="J14" s="37" t="n"/>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>Banco o entidad financiera</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="inlineStr">
+        <is>
+          <t>Complex networks-based anomaly detection for financial transactions in anti-money laundering</t>
+        </is>
+      </c>
+      <c r="F14" s="37" t="inlineStr">
+        <is>
+          <t>Oliveira, Sant'Anna y Ferreira</t>
+        </is>
+      </c>
+      <c r="G14" s="38" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H14" s="37" t="inlineStr">
+        <is>
+          <t>Forensic Science International: Digital Investigation</t>
+        </is>
+      </c>
+      <c r="I14" s="37" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.fsidi.2025.302005</t>
+        </is>
+      </c>
+      <c r="J14" s="37" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
       <c r="K14" s="38" t="n"/>
       <c r="L14" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M14" s="39" t="n"/>
@@ -1702,17 +1774,43 @@
           <t>Joaquín</t>
         </is>
       </c>
-      <c r="D15" s="37" t="n"/>
-      <c r="E15" s="37" t="n"/>
-      <c r="F15" s="37" t="n"/>
-      <c r="G15" s="38" t="n"/>
-      <c r="H15" s="37" t="n"/>
-      <c r="I15" s="37" t="n"/>
-      <c r="J15" s="37" t="n"/>
+      <c r="D15" s="37" t="inlineStr">
+        <is>
+          <t>Banco o entidad financiera</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
+        <is>
+          <t>SMoTeF: Smurf money laundering detection using temporal order and flow analysis</t>
+        </is>
+      </c>
+      <c r="F15" s="37" t="inlineStr">
+        <is>
+          <t>Shadrooh y Nørvåg</t>
+        </is>
+      </c>
+      <c r="G15" s="38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H15" s="37" t="inlineStr">
+        <is>
+          <t>Applied Intelligence</t>
+        </is>
+      </c>
+      <c r="I15" s="37" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10489-024-05545-4</t>
+        </is>
+      </c>
+      <c r="J15" s="37" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
       <c r="K15" s="38" t="n"/>
       <c r="L15" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M15" s="39" t="n"/>

--- a/Joaquin/Matriz_Joaquin.xlsx
+++ b/Joaquin/Matriz_Joaquin.xlsx
@@ -495,17 +495,12 @@
     </comment>
     <comment ref="E13" authorId="3" shapeId="0">
       <text>
-        <t>LECTURA COMPLETA: CUMPLE (IEEE Access 2025, Q1). Özyeğin Univ., Turquía. AMLPD: embeddings NO supervisados (PageRank personalizado + difusión) sobre el grafo de transacciones y luego un clasificador. Datos reales de un gran banco turco (~10 M nodos, 23 M aristas, 1 mes) + AMLSim (sintético) + 2 benchmarks. F1 0,85 en el grafo de 10 M nodos; supera a GNN supervisadas y a no supervisados (DBSCAN). Limitación: requiere grafo de transferencias entre cuentas (Perumoney no lo tiene). Responde P3, P4, P5.</t>
+        <t>LECTURA COMPLETA: CUMPLE (IEEE Access, Q1 2025). Univ. de Salford, Reino Unido. Datos reales (FinCEN Files, SAR filtrados 1999-2017). Benchmark supervisado (RF/XGBoost AUC ~0,97) vs no supervisado (Isolation Forest/One-Class SVM &lt; 0,75): útil para P4. Debilidades: la etiqueta la construyen los autores con su score de riesgo (parcialmente circular), test de 41 casos, transacciones banco-a-banco. Viene de Candidatos fila 55.</t>
       </text>
     </comment>
     <comment ref="E14" authorId="3" shapeId="0">
       <text>
-        <t>LECTURA COMPLETA: CUMPLE en lo formal; falta cuartil (Forensic Science International: Digital Investigation). Univ. Federal de Bahía, Brasil. Datos REALES de una investigación de lavado del Ministerio Público de Sergipe (sistema SIMBA): 9 322 transacciones de 4 investigados, 767 cuentas destino. NO supervisado: detección de anomalías con GNN + comunidades, densidad y ciclos; K-means/K-prototypes para perfiles. Validación sin etiquetas con Silhouette (0,83) y Davies-Bouldin (1,59) en test, con validación cruzada. Relevante para P5 (cómo validar sin casos etiquetados) y P2/P3. Limitación: muestra pequeña (4 personas) y validación solo con métricas internas.</t>
-      </text>
-    </comment>
-    <comment ref="E15" authorId="3" shapeId="0">
-      <text>
-        <t>LECTURA COMPLETA: CUMPLE en lo formal; falta cuartil (Applied Intelligence). NTNU, Noruega. SMoTeF detecta FRACCIONAMIENTO (smurfing) con flujo temporal máximo respetando el orden de las transacciones; reduce los falsos positivos de los detectores de patrones en grafos. Evaluado inyectando patrones de smurfing en datos reales (Czech Financial Dataset, ~280 mil transacciones bancarias; DARPA; Enron), con precision/recall/F1 frente al estado del arte. Muy relevante para la causa C2 (operaciones fraccionadas bajo el umbral de USD 5 000). Limitación: los casos positivos son inyectados (sintéticos) y requiere grafo origen-destino.</t>
+        <t>LECTURA COMPLETA: cumple en lo formal (JMLC 2023, Q2), pero débil. Capitol Technology Univ., EE. UU. Árbol de decisión y otros clasificadores para predecir si una transacción sobre el umbral debe reportarse (SAR); identifica los atributos relevantes (P2). Datos SINTÉTICOS (transacciones públicas modificadas), un solo escenario. Año 2023 (límite CE2). Viene de Candidatos fila 43.</t>
       </text>
     </comment>
   </commentList>
@@ -1641,16 +1636,16 @@
       </c>
       <c r="E13" s="37" t="inlineStr">
         <is>
-          <t>PageRank-Based Unsupervised Deep Vertex Representations for Anti-Money Laundering Detection</t>
+          <t>Machine Learning and Network Analysis for Cross-Border Suspicious Transaction Detection: Evidence From the FinCEN Files</t>
         </is>
       </c>
       <c r="F13" s="37" t="inlineStr">
         <is>
-          <t>Gezici y Sefer</t>
+          <t>Ejime, Kosemani y Onyeorueka</t>
         </is>
       </c>
       <c r="G13" s="38" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H13" s="37" t="inlineStr">
         <is>
@@ -1659,12 +1654,12 @@
       </c>
       <c r="I13" s="37" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ACCESS.2025.3634197</t>
+          <t>https://doi.org/10.1109/ACCESS.2026.3685103</t>
         </is>
       </c>
       <c r="J13" s="37" t="inlineStr">
         <is>
-          <t>Turquía</t>
+          <t>Reino Unido</t>
         </is>
       </c>
       <c r="K13" s="38" t="inlineStr">
@@ -1713,33 +1708,37 @@
       </c>
       <c r="E14" s="37" t="inlineStr">
         <is>
-          <t>Complex networks-based anomaly detection for financial transactions in anti-money laundering</t>
+          <t>The use of predictive modeling to identify relevant features for suspicious activity reporting</t>
         </is>
       </c>
       <c r="F14" s="37" t="inlineStr">
         <is>
-          <t>Oliveira, Sant'Anna y Ferreira</t>
+          <t>Hayble-Gomes</t>
         </is>
       </c>
       <c r="G14" s="38" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H14" s="37" t="inlineStr">
         <is>
-          <t>Forensic Science International: Digital Investigation</t>
+          <t>Journal of Money Laundering Control</t>
         </is>
       </c>
       <c r="I14" s="37" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.fsidi.2025.302005</t>
+          <t>https://doi.org/10.1108/JMLC-02-2022-0034</t>
         </is>
       </c>
       <c r="J14" s="37" t="inlineStr">
         <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="K14" s="38" t="n"/>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="K14" s="38" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="L14" s="38" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1774,43 +1773,17 @@
           <t>Joaquín</t>
         </is>
       </c>
-      <c r="D15" s="37" t="inlineStr">
-        <is>
-          <t>Banco o entidad financiera</t>
-        </is>
-      </c>
-      <c r="E15" s="37" t="inlineStr">
-        <is>
-          <t>SMoTeF: Smurf money laundering detection using temporal order and flow analysis</t>
-        </is>
-      </c>
-      <c r="F15" s="37" t="inlineStr">
-        <is>
-          <t>Shadrooh y Nørvåg</t>
-        </is>
-      </c>
-      <c r="G15" s="38" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H15" s="37" t="inlineStr">
-        <is>
-          <t>Applied Intelligence</t>
-        </is>
-      </c>
-      <c r="I15" s="37" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s10489-024-05545-4</t>
-        </is>
-      </c>
-      <c r="J15" s="37" t="inlineStr">
-        <is>
-          <t>Noruega</t>
-        </is>
-      </c>
+      <c r="D15" s="37" t="n"/>
+      <c r="E15" s="37" t="n"/>
+      <c r="F15" s="37" t="n"/>
+      <c r="G15" s="38" t="n"/>
+      <c r="H15" s="37" t="n"/>
+      <c r="I15" s="37" t="n"/>
+      <c r="J15" s="37" t="n"/>
       <c r="K15" s="38" t="n"/>
       <c r="L15" s="38" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M15" s="39" t="n"/>

--- a/Joaquin/Matriz_Joaquin.xlsx
+++ b/Joaquin/Matriz_Joaquin.xlsx
@@ -418,6 +418,7 @@
     <author>Claude (10-10-2026)</author>
     <author>Claude (lectura completa 10-10-2026)</author>
     <author>Claude (11-10-2026)</author>
+    <author>Claude (12-10-2026)</author>
   </authors>
   <commentList>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -501,6 +502,16 @@
     <comment ref="E14" authorId="3" shapeId="0">
       <text>
         <t>LECTURA COMPLETA: cumple en lo formal (JMLC 2023, Q2), pero débil. Capitol Technology Univ., EE. UU. Árbol de decisión y otros clasificadores para predecir si una transacción sobre el umbral debe reportarse (SAR); identifica los atributos relevantes (P2). Datos SINTÉTICOS (transacciones públicas modificadas), un solo escenario. Año 2023 (límite CE2). Viene de Candidatos fila 43.</t>
+      </text>
+    </comment>
+    <comment ref="E15" authorId="4" shapeId="0">
+      <text>
+        <t>LECTURA COMPLETA: cumple (Q1, categoría Multidisciplinary). IT University of Copenhagen, Dinamarca. Propone un escenario de evaluación realista en dos pasos (cada banco marca sus operaciones; la autoridad analiza solo lo marcado). Con datos SINTÉTICOS (IBM-AML) y modelos de grafos (FraudGT, GatedGCN): el F1 cae de 0,32/0,71 a 0,12/0,56 en el escenario realista, y usar un modelo más simple en un paso lo sube a 0,49/0,85. Útil para P5 (validación realista) y P4. Viene de Candidatos fila 52.</t>
+      </text>
+    </comment>
+    <comment ref="E16" authorId="4" shapeId="0">
+      <text>
+        <t>LECTURA COMPLETA: cumple (Q2), pero débil. Royal Roads University, Canadá. NB, RF, regresión logística, CatBoost y red neuronal sobre datos SIMULADOS de bancos de Medio Oriente (2 340 observaciones). Accuracy ~77 % (NB y RF), ANN 80 %; RF: precisión 0,87, recall 0,72. Útil para P2: hora del día, día de la semana, tipo (cash-in/transfer-out) y etapa del lavado como variables. Viene de Candidatos fila 27.</t>
       </text>
     </comment>
   </commentList>
@@ -1773,17 +1784,47 @@
           <t>Joaquín</t>
         </is>
       </c>
-      <c r="D15" s="37" t="n"/>
-      <c r="E15" s="37" t="n"/>
-      <c r="F15" s="37" t="n"/>
-      <c r="G15" s="38" t="n"/>
-      <c r="H15" s="37" t="n"/>
-      <c r="I15" s="37" t="n"/>
-      <c r="J15" s="37" t="n"/>
-      <c r="K15" s="38" t="n"/>
+      <c r="D15" s="37" t="inlineStr">
+        <is>
+          <t>Banco o entidad financiera</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
+        <is>
+          <t>Evaluating fraud detection algorithms in a decentralized scenario</t>
+        </is>
+      </c>
+      <c r="F15" s="37" t="inlineStr">
+        <is>
+          <t>Gige, Buschmann Alsbirk y Coscia</t>
+        </is>
+      </c>
+      <c r="G15" s="38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H15" s="37" t="inlineStr">
+        <is>
+          <t>Royal Society Open Science</t>
+        </is>
+      </c>
+      <c r="I15" s="37" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1098/rsos.251922</t>
+        </is>
+      </c>
+      <c r="J15" s="37" t="inlineStr">
+        <is>
+          <t>Dinamarca</t>
+        </is>
+      </c>
+      <c r="K15" s="38" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="L15" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M15" s="39" t="n"/>
@@ -1815,17 +1856,47 @@
           <t>Joaquín</t>
         </is>
       </c>
-      <c r="D16" s="37" t="n"/>
-      <c r="E16" s="37" t="n"/>
-      <c r="F16" s="37" t="n"/>
-      <c r="G16" s="38" t="n"/>
-      <c r="H16" s="37" t="n"/>
-      <c r="I16" s="37" t="n"/>
-      <c r="J16" s="37" t="n"/>
-      <c r="K16" s="38" t="n"/>
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>Banco o entidad financiera</t>
+        </is>
+      </c>
+      <c r="E16" s="37" t="inlineStr">
+        <is>
+          <t>Predicting Money Laundering Using Machine Learning and Artificial Neural Networks Algorithms in Banks</t>
+        </is>
+      </c>
+      <c r="F16" s="37" t="inlineStr">
+        <is>
+          <t>Lokanan</t>
+        </is>
+      </c>
+      <c r="G16" s="38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H16" s="37" t="inlineStr">
+        <is>
+          <t>Journal of Applied Security Research</t>
+        </is>
+      </c>
+      <c r="I16" s="37" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/19361610.2022.2114744</t>
+        </is>
+      </c>
+      <c r="J16" s="37" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="K16" s="38" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="L16" s="38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M16" s="39" t="n"/>
